--- a/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
+++ b/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
@@ -34,6 +34,7 @@
     <definedName name="Finance_Rate">Assumptions!$B$25</definedName>
     <definedName name="LTC">Assumptions!$B$26</definedName>
     <definedName name="Duration">Assumptions!$B$27</definedName>
+    <definedName name="TotalGSF">Assumptions!$B$5</definedName>
     <definedName name="ConstructionSubtotal">'Hard Costs'!$E$27</definedName>
     <definedName name="TotalHardCosts">'Hard Costs'!$E$38</definedName>
     <definedName name="TotalSoftCosts">'Soft Costs'!$B$20</definedName>
@@ -589,10 +590,10 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -605,11 +606,10 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2025-11-06 00:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Generated: 2025-11-06 00:43</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -674,11 +674,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -697,7 +696,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -742,7 +740,6 @@
         <v/>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -797,10 +794,10 @@
   <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -810,7 +807,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -818,7 +814,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -828,10 +823,8 @@
       <c r="B5" s="12" t="n">
         <v>108675</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -857,13 +850,10 @@
       <c r="B7" t="n">
         <v>50</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
@@ -871,7 +861,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -938,10 +927,8 @@
       <c r="B14" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="C14" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -949,7 +936,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
@@ -957,7 +943,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -1123,9 +1108,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
@@ -1365,7 +1347,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
@@ -1409,13 +1390,6 @@
   </sheetPr>
   <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
@@ -1424,7 +1398,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -1466,8 +1439,9 @@
       <c r="C4" s="18" t="n">
         <v>10.53</v>
       </c>
-      <c r="D4" s="12" t="n">
-        <v>108675</v>
+      <c r="D4" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E4" s="3">
         <f>C4*D4</f>
@@ -1488,8 +1462,9 @@
       <c r="C5" s="18" t="n">
         <v>4.56</v>
       </c>
-      <c r="D5" s="12" t="n">
-        <v>108675</v>
+      <c r="D5" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E5" s="3">
         <f>C5*D5</f>
@@ -1510,8 +1485,9 @@
       <c r="C6" s="18" t="n">
         <v>39.47</v>
       </c>
-      <c r="D6" s="12" t="n">
-        <v>108675</v>
+      <c r="D6" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E6" s="3">
         <f>C6*D6</f>
@@ -1532,8 +1508,9 @@
       <c r="C7" s="18" t="n">
         <v>2.46</v>
       </c>
-      <c r="D7" s="12" t="n">
-        <v>108675</v>
+      <c r="D7" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E7" s="3">
         <f>C7*D7</f>
@@ -1554,8 +1531,9 @@
       <c r="C8" s="18" t="n">
         <v>7.45</v>
       </c>
-      <c r="D8" s="12" t="n">
-        <v>108675</v>
+      <c r="D8" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E8" s="3">
         <f>C8*D8</f>
@@ -1576,8 +1554,9 @@
       <c r="C9" s="18" t="n">
         <v>2.81</v>
       </c>
-      <c r="D9" s="12" t="n">
-        <v>108675</v>
+      <c r="D9" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E9" s="3">
         <f>C9*D9</f>
@@ -1598,8 +1577,9 @@
       <c r="C10" s="18" t="n">
         <v>19.3</v>
       </c>
-      <c r="D10" s="12" t="n">
-        <v>108675</v>
+      <c r="D10" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E10" s="3">
         <f>C10*D10</f>
@@ -1620,8 +1600,9 @@
       <c r="C11" s="18" t="n">
         <v>24.55</v>
       </c>
-      <c r="D11" s="12" t="n">
-        <v>108675</v>
+      <c r="D11" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E11" s="3">
         <f>C11*D11</f>
@@ -1642,8 +1623,9 @@
       <c r="C12" s="18" t="n">
         <v>36.83</v>
       </c>
-      <c r="D12" s="12" t="n">
-        <v>108675</v>
+      <c r="D12" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E12" s="3">
         <f>C12*D12</f>
@@ -1664,8 +1646,9 @@
       <c r="C13" s="18" t="n">
         <v>3.95</v>
       </c>
-      <c r="D13" s="12" t="n">
-        <v>108675</v>
+      <c r="D13" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E13" s="3">
         <f>C13*D13</f>
@@ -1686,8 +1669,9 @@
       <c r="C14" s="18" t="n">
         <v>3.33</v>
       </c>
-      <c r="D14" s="12" t="n">
-        <v>108675</v>
+      <c r="D14" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E14" s="3">
         <f>C14*D14</f>
@@ -1708,8 +1692,9 @@
       <c r="C15" s="18" t="n">
         <v>1.05</v>
       </c>
-      <c r="D15" s="12" t="n">
-        <v>108675</v>
+      <c r="D15" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E15" s="3">
         <f>C15*D15</f>
@@ -1730,8 +1715,9 @@
       <c r="C16" s="18" t="n">
         <v>1.58</v>
       </c>
-      <c r="D16" s="12" t="n">
-        <v>108675</v>
+      <c r="D16" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E16" s="3">
         <f>C16*D16</f>
@@ -1752,8 +1738,9 @@
       <c r="C17" s="18" t="n">
         <v>2.72</v>
       </c>
-      <c r="D17" s="12" t="n">
-        <v>108675</v>
+      <c r="D17" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E17" s="3">
         <f>C17*D17</f>
@@ -1774,8 +1761,9 @@
       <c r="C18" s="18" t="n">
         <v>6.58</v>
       </c>
-      <c r="D18" s="12" t="n">
-        <v>108675</v>
+      <c r="D18" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E18" s="3">
         <f>C18*D18</f>
@@ -1796,8 +1784,9 @@
       <c r="C19" s="18" t="n">
         <v>8.77</v>
       </c>
-      <c r="D19" s="12" t="n">
-        <v>108675</v>
+      <c r="D19" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E19" s="3">
         <f>C19*D19</f>
@@ -1818,8 +1807,9 @@
       <c r="C20" s="18" t="n">
         <v>13.15</v>
       </c>
-      <c r="D20" s="12" t="n">
-        <v>108675</v>
+      <c r="D20" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E20" s="3">
         <f>C20*D20</f>
@@ -1840,8 +1830,9 @@
       <c r="C21" s="18" t="n">
         <v>13.15</v>
       </c>
-      <c r="D21" s="12" t="n">
-        <v>108675</v>
+      <c r="D21" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E21" s="3">
         <f>C21*D21</f>
@@ -1862,8 +1853,9 @@
       <c r="C22" s="18" t="n">
         <v>1.75</v>
       </c>
-      <c r="D22" s="12" t="n">
-        <v>108675</v>
+      <c r="D22" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E22" s="3">
         <f>C22*D22</f>
@@ -1884,8 +1876,9 @@
       <c r="C23" s="18" t="n">
         <v>1.75</v>
       </c>
-      <c r="D23" s="12" t="n">
-        <v>108675</v>
+      <c r="D23" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E23" s="3">
         <f>C23*D23</f>
@@ -1906,8 +1899,9 @@
       <c r="C24" s="18" t="n">
         <v>3.68</v>
       </c>
-      <c r="D24" s="12" t="n">
-        <v>108675</v>
+      <c r="D24" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E24" s="3">
         <f>C24*D24</f>
@@ -1928,8 +1922,9 @@
       <c r="C25" s="18" t="n">
         <v>3.51</v>
       </c>
-      <c r="D25" s="12" t="n">
-        <v>108675</v>
+      <c r="D25" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E25" s="3">
         <f>C25*D25</f>
@@ -1950,8 +1945,9 @@
       <c r="C26" s="18" t="n">
         <v>2.81</v>
       </c>
-      <c r="D26" s="12" t="n">
-        <v>108675</v>
+      <c r="D26" s="12">
+        <f>TotalGSF</f>
+        <v/>
       </c>
       <c r="E26" s="3">
         <f>C26*D26</f>
@@ -1969,7 +1965,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
@@ -2000,7 +1995,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="B32" s="16" t="inlineStr">
         <is>
@@ -2012,7 +2006,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
@@ -2058,7 +2051,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -2097,12 +2089,6 @@
   </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
@@ -2118,7 +2104,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -2225,7 +2210,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -2373,7 +2357,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -2386,7 +2369,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
@@ -2443,14 +2425,6 @@
   </sheetPr>
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
@@ -2459,7 +2433,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -2592,7 +2565,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -2624,13 +2596,6 @@
   </sheetPr>
   <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -2646,7 +2611,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -2697,7 +2661,6 @@
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
@@ -2840,7 +2803,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
@@ -3010,7 +2972,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="26" t="inlineStr">
         <is>
@@ -3023,7 +2984,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
@@ -3229,7 +3189,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
@@ -3305,7 +3264,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
@@ -3415,18 +3373,6 @@
   </sheetPr>
   <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
@@ -3442,7 +3388,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3471,7 +3416,7 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>Pre-Sales Revenue</t>
+          <t>Pre-Sales Revenue (25%)</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
@@ -3516,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="3">
-        <f>E5*(TotalRevenue/50)*0.20</f>
+        <f>E5*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G5" s="3">
@@ -3556,7 +3501,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="3">
-        <f>E6*(TotalRevenue/50)*0.20</f>
+        <f>E6*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G6" s="3">
@@ -3596,7 +3541,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="3">
-        <f>E7*(TotalRevenue/50)*0.20</f>
+        <f>E7*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G7" s="3">
@@ -3636,7 +3581,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="3">
-        <f>E8*(TotalRevenue/50)*0.20</f>
+        <f>E8*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G8" s="3">
@@ -3676,7 +3621,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="3">
-        <f>E9*(TotalRevenue/50)*0.20</f>
+        <f>(E9*(TotalRevenue/50)*0.25)+(SUM(E5:E8)*(TotalRevenue/50)*0.25)</f>
         <v/>
       </c>
       <c r="G9" s="3">
@@ -3717,7 +3662,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="3">
-        <f>E10*(TotalRevenue/50)*0.20</f>
+        <f>E10*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G10" s="3">
@@ -3757,7 +3702,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="3">
-        <f>E11*(TotalRevenue/50)*0.20</f>
+        <f>E11*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G11" s="3">
@@ -3797,7 +3742,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="3">
-        <f>E12*(TotalRevenue/50)*0.20</f>
+        <f>E12*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G12" s="3">
@@ -3837,7 +3782,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="3">
-        <f>E13*(TotalRevenue/50)*0.20</f>
+        <f>(E13*(TotalRevenue/50)*0.25)+(SUM(E5:E12)*(TotalRevenue/50)*0.25)</f>
         <v/>
       </c>
       <c r="G13" s="3">
@@ -3877,7 +3822,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="3">
-        <f>E14*(TotalRevenue/50)*0.20</f>
+        <f>E14*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G14" s="3">
@@ -3917,7 +3862,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3">
-        <f>E15*(TotalRevenue/50)*0.20</f>
+        <f>E15*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G15" s="3">
@@ -3957,7 +3902,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3">
-        <f>E16*(TotalRevenue/50)*0.20</f>
+        <f>E16*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G16" s="3">
@@ -3997,7 +3942,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="3">
-        <f>E17*(TotalRevenue/50)*0.20</f>
+        <f>E17*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G17" s="3">
@@ -4037,7 +3982,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="3">
-        <f>E18*(TotalRevenue/50)*0.20</f>
+        <f>E18*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G18" s="3">
@@ -4077,7 +4022,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="3">
-        <f>E19*(TotalRevenue/50)*0.20</f>
+        <f>E19*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G19" s="3">
@@ -4117,7 +4062,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="3">
-        <f>E20*(TotalRevenue/50)*0.20</f>
+        <f>E20*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G20" s="3">
@@ -4157,7 +4102,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="3">
-        <f>E21*(TotalRevenue/50)*0.20</f>
+        <f>E21*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G21" s="3">
@@ -4197,7 +4142,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="3">
-        <f>E22*(TotalRevenue/50)*0.20</f>
+        <f>E22*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G22" s="3">
@@ -4237,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="3">
-        <f>E23*(TotalRevenue/50)*0.20</f>
+        <f>E23*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G23" s="3">
@@ -4277,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="3">
-        <f>E24*(TotalRevenue/50)*0.20</f>
+        <f>E24*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G24" s="3">
@@ -4317,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="3">
-        <f>E25*(TotalRevenue/50)*0.20</f>
+        <f>E25*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G25" s="3">
@@ -4357,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="3">
-        <f>E26*(TotalRevenue/50)*0.20</f>
+        <f>E26*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G26" s="3">
@@ -4397,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="3">
-        <f>E27*(TotalRevenue/50)*0.20</f>
+        <f>E27*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G27" s="3">
@@ -4437,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="3">
-        <f>E28*(TotalRevenue/50)*0.20</f>
+        <f>E28*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G28" s="3">
@@ -4457,7 +4402,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
@@ -4481,7 +4425,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="31" t="inlineStr">
         <is>
@@ -4510,16 +4453,6 @@
   </sheetPr>
   <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
@@ -4542,7 +4475,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -5412,7 +5344,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
@@ -5454,7 +5385,6 @@
         <v/>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -5470,8 +5400,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
         <is>
@@ -5671,7 +5599,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
@@ -5711,10 +5638,6 @@
   </sheetPr>
   <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="inlineStr">
@@ -5723,7 +5646,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>

--- a/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
+++ b/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
@@ -606,7 +606,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2025-11-06 00:43</t>
+          <t>Generated: 2025-11-06 01:03</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3416,25 +3416,30 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>Pre-Sales Revenue (25%)</t>
+          <t>Pre-Sales Payment</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
+          <t>Usable (90%)</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
           <t>Total Cash In</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>Net Cash Flow</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>Cumulative Cash</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>Bridge Loan Need</t>
         </is>
@@ -3465,19 +3470,23 @@
         <v/>
       </c>
       <c r="G5" s="3">
-        <f>D5+F5</f>
+        <f>F5*0.90</f>
         <v/>
       </c>
       <c r="H5" s="3">
-        <f>G5-C5</f>
+        <f>D5+G5</f>
         <v/>
       </c>
       <c r="I5" s="3">
-        <f>H5</f>
-        <v/>
-      </c>
-      <c r="J5" s="30">
-        <f>IF(I5&lt;0,-I5,0)</f>
+        <f>H5-C5</f>
+        <v/>
+      </c>
+      <c r="J5" s="3">
+        <f>I5</f>
+        <v/>
+      </c>
+      <c r="K5" s="30">
+        <f>IF(J5&lt;0,-J5,0)</f>
         <v/>
       </c>
     </row>
@@ -3505,19 +3514,23 @@
         <v/>
       </c>
       <c r="G6" s="3">
-        <f>D6+F6</f>
+        <f>F6*0.90</f>
         <v/>
       </c>
       <c r="H6" s="3">
-        <f>G6-C6</f>
+        <f>D6+G6</f>
         <v/>
       </c>
       <c r="I6" s="3">
-        <f>I5+H6</f>
-        <v/>
-      </c>
-      <c r="J6" s="30">
-        <f>IF(I6&lt;0,-I6,0)</f>
+        <f>H6-C6</f>
+        <v/>
+      </c>
+      <c r="J6" s="3">
+        <f>J5+I6</f>
+        <v/>
+      </c>
+      <c r="K6" s="30">
+        <f>IF(J6&lt;0,-J6,0)</f>
         <v/>
       </c>
     </row>
@@ -3545,19 +3558,23 @@
         <v/>
       </c>
       <c r="G7" s="3">
-        <f>D7+F7</f>
+        <f>F7*0.90</f>
         <v/>
       </c>
       <c r="H7" s="3">
-        <f>G7-C7</f>
+        <f>D7+G7</f>
         <v/>
       </c>
       <c r="I7" s="3">
-        <f>I6+H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="30">
-        <f>IF(I7&lt;0,-I7,0)</f>
+        <f>H7-C7</f>
+        <v/>
+      </c>
+      <c r="J7" s="3">
+        <f>J6+I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="30">
+        <f>IF(J7&lt;0,-J7,0)</f>
         <v/>
       </c>
     </row>
@@ -3585,19 +3602,23 @@
         <v/>
       </c>
       <c r="G8" s="3">
-        <f>D8+F8</f>
+        <f>F8*0.90</f>
         <v/>
       </c>
       <c r="H8" s="3">
-        <f>G8-C8</f>
+        <f>D8+G8</f>
         <v/>
       </c>
       <c r="I8" s="3">
-        <f>I7+H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="30">
-        <f>IF(I8&lt;0,-I8,0)</f>
+        <f>H8-C8</f>
+        <v/>
+      </c>
+      <c r="J8" s="3">
+        <f>J7+I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="30">
+        <f>IF(J8&lt;0,-J8,0)</f>
         <v/>
       </c>
     </row>
@@ -3621,23 +3642,27 @@
         <v>3</v>
       </c>
       <c r="F9" s="3">
-        <f>(E9*(TotalRevenue/50)*0.25)+(SUM(E5:E8)*(TotalRevenue/50)*0.25)</f>
+        <f>(E9*(TotalRevenue/50)*0.25)+(SUM($E$5:E8)*(TotalRevenue/50)*0.25)</f>
         <v/>
       </c>
       <c r="G9" s="3">
-        <f>D9+F9</f>
+        <f>F9*0.90</f>
         <v/>
       </c>
       <c r="H9" s="3">
-        <f>G9-C9</f>
+        <f>D9+G9</f>
         <v/>
       </c>
       <c r="I9" s="3">
-        <f>I8+H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="30">
-        <f>IF(I9&lt;0,-I9,0)</f>
+        <f>H9-C9</f>
+        <v/>
+      </c>
+      <c r="J9" s="3">
+        <f>J8+I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="30">
+        <f>IF(J9&lt;0,-J9,0)</f>
         <v/>
       </c>
     </row>
@@ -3666,19 +3691,23 @@
         <v/>
       </c>
       <c r="G10" s="3">
-        <f>D10+F10</f>
+        <f>F10*0.90</f>
         <v/>
       </c>
       <c r="H10" s="3">
-        <f>G10-C10</f>
+        <f>D10+G10</f>
         <v/>
       </c>
       <c r="I10" s="3">
-        <f>I9+H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="30">
-        <f>IF(I10&lt;0,-I10,0)</f>
+        <f>H10-C10</f>
+        <v/>
+      </c>
+      <c r="J10" s="3">
+        <f>J9+I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="30">
+        <f>IF(J10&lt;0,-J10,0)</f>
         <v/>
       </c>
     </row>
@@ -3706,19 +3735,23 @@
         <v/>
       </c>
       <c r="G11" s="3">
-        <f>D11+F11</f>
+        <f>F11*0.90</f>
         <v/>
       </c>
       <c r="H11" s="3">
-        <f>G11-C11</f>
+        <f>D11+G11</f>
         <v/>
       </c>
       <c r="I11" s="3">
-        <f>I10+H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="30">
-        <f>IF(I11&lt;0,-I11,0)</f>
+        <f>H11-C11</f>
+        <v/>
+      </c>
+      <c r="J11" s="3">
+        <f>J10+I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="30">
+        <f>IF(J11&lt;0,-J11,0)</f>
         <v/>
       </c>
     </row>
@@ -3746,19 +3779,23 @@
         <v/>
       </c>
       <c r="G12" s="3">
-        <f>D12+F12</f>
+        <f>F12*0.90</f>
         <v/>
       </c>
       <c r="H12" s="3">
-        <f>G12-C12</f>
+        <f>D12+G12</f>
         <v/>
       </c>
       <c r="I12" s="3">
-        <f>I11+H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="30">
-        <f>IF(I12&lt;0,-I12,0)</f>
+        <f>H12-C12</f>
+        <v/>
+      </c>
+      <c r="J12" s="3">
+        <f>J11+I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="30">
+        <f>IF(J12&lt;0,-J12,0)</f>
         <v/>
       </c>
     </row>
@@ -3782,23 +3819,27 @@
         <v>4</v>
       </c>
       <c r="F13" s="3">
-        <f>(E13*(TotalRevenue/50)*0.25)+(SUM(E5:E12)*(TotalRevenue/50)*0.25)</f>
+        <f>E13*(TotalRevenue/50)*0.25</f>
         <v/>
       </c>
       <c r="G13" s="3">
-        <f>D13+F13</f>
+        <f>F13*0.90</f>
         <v/>
       </c>
       <c r="H13" s="3">
-        <f>G13-C13</f>
+        <f>D13+G13</f>
         <v/>
       </c>
       <c r="I13" s="3">
-        <f>I12+H13</f>
-        <v/>
-      </c>
-      <c r="J13" s="30">
-        <f>IF(I13&lt;0,-I13,0)</f>
+        <f>H13-C13</f>
+        <v/>
+      </c>
+      <c r="J13" s="3">
+        <f>J12+I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="30">
+        <f>IF(J13&lt;0,-J13,0)</f>
         <v/>
       </c>
     </row>
@@ -3826,19 +3867,23 @@
         <v/>
       </c>
       <c r="G14" s="3">
-        <f>D14+F14</f>
+        <f>F14*0.90</f>
         <v/>
       </c>
       <c r="H14" s="3">
-        <f>G14-C14</f>
+        <f>D14+G14</f>
         <v/>
       </c>
       <c r="I14" s="3">
-        <f>I13+H14</f>
-        <v/>
-      </c>
-      <c r="J14" s="30">
-        <f>IF(I14&lt;0,-I14,0)</f>
+        <f>H14-C14</f>
+        <v/>
+      </c>
+      <c r="J14" s="3">
+        <f>J13+I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>IF(J14&lt;0,-J14,0)</f>
         <v/>
       </c>
     </row>
@@ -3866,19 +3911,23 @@
         <v/>
       </c>
       <c r="G15" s="3">
-        <f>D15+F15</f>
+        <f>F15*0.90</f>
         <v/>
       </c>
       <c r="H15" s="3">
-        <f>G15-C15</f>
+        <f>D15+G15</f>
         <v/>
       </c>
       <c r="I15" s="3">
-        <f>I14+H15</f>
-        <v/>
-      </c>
-      <c r="J15" s="30">
-        <f>IF(I15&lt;0,-I15,0)</f>
+        <f>H15-C15</f>
+        <v/>
+      </c>
+      <c r="J15" s="3">
+        <f>J14+I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="30">
+        <f>IF(J15&lt;0,-J15,0)</f>
         <v/>
       </c>
     </row>
@@ -3906,19 +3955,23 @@
         <v/>
       </c>
       <c r="G16" s="3">
-        <f>D16+F16</f>
+        <f>F16*0.90</f>
         <v/>
       </c>
       <c r="H16" s="3">
-        <f>G16-C16</f>
+        <f>D16+G16</f>
         <v/>
       </c>
       <c r="I16" s="3">
-        <f>I15+H16</f>
-        <v/>
-      </c>
-      <c r="J16" s="30">
-        <f>IF(I16&lt;0,-I16,0)</f>
+        <f>H16-C16</f>
+        <v/>
+      </c>
+      <c r="J16" s="3">
+        <f>J15+I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="30">
+        <f>IF(J16&lt;0,-J16,0)</f>
         <v/>
       </c>
     </row>
@@ -3946,19 +3999,23 @@
         <v/>
       </c>
       <c r="G17" s="3">
-        <f>D17+F17</f>
+        <f>F17*0.90</f>
         <v/>
       </c>
       <c r="H17" s="3">
-        <f>G17-C17</f>
+        <f>D17+G17</f>
         <v/>
       </c>
       <c r="I17" s="3">
-        <f>I16+H17</f>
-        <v/>
-      </c>
-      <c r="J17" s="30">
-        <f>IF(I17&lt;0,-I17,0)</f>
+        <f>H17-C17</f>
+        <v/>
+      </c>
+      <c r="J17" s="3">
+        <f>J16+I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="30">
+        <f>IF(J17&lt;0,-J17,0)</f>
         <v/>
       </c>
     </row>
@@ -3986,19 +4043,23 @@
         <v/>
       </c>
       <c r="G18" s="3">
-        <f>D18+F18</f>
+        <f>F18*0.90</f>
         <v/>
       </c>
       <c r="H18" s="3">
-        <f>G18-C18</f>
+        <f>D18+G18</f>
         <v/>
       </c>
       <c r="I18" s="3">
-        <f>I17+H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="30">
-        <f>IF(I18&lt;0,-I18,0)</f>
+        <f>H18-C18</f>
+        <v/>
+      </c>
+      <c r="J18" s="3">
+        <f>J17+I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="30">
+        <f>IF(J18&lt;0,-J18,0)</f>
         <v/>
       </c>
     </row>
@@ -4022,23 +4083,27 @@
         <v>2</v>
       </c>
       <c r="F19" s="3">
-        <f>E19*(TotalRevenue/50)*0.25</f>
+        <f>(E19*(TotalRevenue/50)*0.25)+(SUM($E$5:E18)*(TotalRevenue/50)*0.25)</f>
         <v/>
       </c>
       <c r="G19" s="3">
-        <f>D19+F19</f>
+        <f>F19*0.90</f>
         <v/>
       </c>
       <c r="H19" s="3">
-        <f>G19-C19</f>
+        <f>D19+G19</f>
         <v/>
       </c>
       <c r="I19" s="3">
-        <f>I18+H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="30">
-        <f>IF(I19&lt;0,-I19,0)</f>
+        <f>H19-C19</f>
+        <v/>
+      </c>
+      <c r="J19" s="3">
+        <f>J18+I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="30">
+        <f>IF(J19&lt;0,-J19,0)</f>
         <v/>
       </c>
     </row>
@@ -4066,19 +4131,23 @@
         <v/>
       </c>
       <c r="G20" s="3">
-        <f>D20+F20</f>
+        <f>F20*0.90</f>
         <v/>
       </c>
       <c r="H20" s="3">
-        <f>G20-C20</f>
+        <f>D20+G20</f>
         <v/>
       </c>
       <c r="I20" s="3">
-        <f>I19+H20</f>
-        <v/>
-      </c>
-      <c r="J20" s="30">
-        <f>IF(I20&lt;0,-I20,0)</f>
+        <f>H20-C20</f>
+        <v/>
+      </c>
+      <c r="J20" s="3">
+        <f>J19+I20</f>
+        <v/>
+      </c>
+      <c r="K20" s="30">
+        <f>IF(J20&lt;0,-J20,0)</f>
         <v/>
       </c>
     </row>
@@ -4106,19 +4175,23 @@
         <v/>
       </c>
       <c r="G21" s="3">
-        <f>D21+F21</f>
+        <f>F21*0.90</f>
         <v/>
       </c>
       <c r="H21" s="3">
-        <f>G21-C21</f>
+        <f>D21+G21</f>
         <v/>
       </c>
       <c r="I21" s="3">
-        <f>I20+H21</f>
-        <v/>
-      </c>
-      <c r="J21" s="30">
-        <f>IF(I21&lt;0,-I21,0)</f>
+        <f>H21-C21</f>
+        <v/>
+      </c>
+      <c r="J21" s="3">
+        <f>J20+I21</f>
+        <v/>
+      </c>
+      <c r="K21" s="30">
+        <f>IF(J21&lt;0,-J21,0)</f>
         <v/>
       </c>
     </row>
@@ -4146,19 +4219,23 @@
         <v/>
       </c>
       <c r="G22" s="3">
-        <f>D22+F22</f>
+        <f>F22*0.90</f>
         <v/>
       </c>
       <c r="H22" s="3">
-        <f>G22-C22</f>
+        <f>D22+G22</f>
         <v/>
       </c>
       <c r="I22" s="3">
-        <f>I21+H22</f>
-        <v/>
-      </c>
-      <c r="J22" s="30">
-        <f>IF(I22&lt;0,-I22,0)</f>
+        <f>H22-C22</f>
+        <v/>
+      </c>
+      <c r="J22" s="3">
+        <f>J21+I22</f>
+        <v/>
+      </c>
+      <c r="K22" s="30">
+        <f>IF(J22&lt;0,-J22,0)</f>
         <v/>
       </c>
     </row>
@@ -4186,19 +4263,23 @@
         <v/>
       </c>
       <c r="G23" s="3">
-        <f>D23+F23</f>
+        <f>F23*0.90</f>
         <v/>
       </c>
       <c r="H23" s="3">
-        <f>G23-C23</f>
+        <f>D23+G23</f>
         <v/>
       </c>
       <c r="I23" s="3">
-        <f>I22+H23</f>
-        <v/>
-      </c>
-      <c r="J23" s="30">
-        <f>IF(I23&lt;0,-I23,0)</f>
+        <f>H23-C23</f>
+        <v/>
+      </c>
+      <c r="J23" s="3">
+        <f>J22+I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="30">
+        <f>IF(J23&lt;0,-J23,0)</f>
         <v/>
       </c>
     </row>
@@ -4226,19 +4307,23 @@
         <v/>
       </c>
       <c r="G24" s="3">
-        <f>D24+F24</f>
+        <f>F24*0.90</f>
         <v/>
       </c>
       <c r="H24" s="3">
-        <f>G24-C24</f>
+        <f>D24+G24</f>
         <v/>
       </c>
       <c r="I24" s="3">
-        <f>I23+H24</f>
-        <v/>
-      </c>
-      <c r="J24" s="30">
-        <f>IF(I24&lt;0,-I24,0)</f>
+        <f>H24-C24</f>
+        <v/>
+      </c>
+      <c r="J24" s="3">
+        <f>J23+I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="30">
+        <f>IF(J24&lt;0,-J24,0)</f>
         <v/>
       </c>
     </row>
@@ -4266,19 +4351,23 @@
         <v/>
       </c>
       <c r="G25" s="3">
-        <f>D25+F25</f>
+        <f>F25*0.90</f>
         <v/>
       </c>
       <c r="H25" s="3">
-        <f>G25-C25</f>
+        <f>D25+G25</f>
         <v/>
       </c>
       <c r="I25" s="3">
-        <f>I24+H25</f>
-        <v/>
-      </c>
-      <c r="J25" s="30">
-        <f>IF(I25&lt;0,-I25,0)</f>
+        <f>H25-C25</f>
+        <v/>
+      </c>
+      <c r="J25" s="3">
+        <f>J24+I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="30">
+        <f>IF(J25&lt;0,-J25,0)</f>
         <v/>
       </c>
     </row>
@@ -4306,19 +4395,23 @@
         <v/>
       </c>
       <c r="G26" s="3">
-        <f>D26+F26</f>
+        <f>F26*0.90</f>
         <v/>
       </c>
       <c r="H26" s="3">
-        <f>G26-C26</f>
+        <f>D26+G26</f>
         <v/>
       </c>
       <c r="I26" s="3">
-        <f>I25+H26</f>
-        <v/>
-      </c>
-      <c r="J26" s="30">
-        <f>IF(I26&lt;0,-I26,0)</f>
+        <f>H26-C26</f>
+        <v/>
+      </c>
+      <c r="J26" s="3">
+        <f>J25+I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="30">
+        <f>IF(J26&lt;0,-J26,0)</f>
         <v/>
       </c>
     </row>
@@ -4346,19 +4439,23 @@
         <v/>
       </c>
       <c r="G27" s="3">
-        <f>D27+F27</f>
+        <f>F27*0.90</f>
         <v/>
       </c>
       <c r="H27" s="3">
-        <f>G27-C27</f>
+        <f>D27+G27</f>
         <v/>
       </c>
       <c r="I27" s="3">
-        <f>I26+H27</f>
-        <v/>
-      </c>
-      <c r="J27" s="30">
-        <f>IF(I27&lt;0,-I27,0)</f>
+        <f>H27-C27</f>
+        <v/>
+      </c>
+      <c r="J27" s="3">
+        <f>J26+I27</f>
+        <v/>
+      </c>
+      <c r="K27" s="30">
+        <f>IF(J27&lt;0,-J27,0)</f>
         <v/>
       </c>
     </row>
@@ -4382,23 +4479,27 @@
         <v>0</v>
       </c>
       <c r="F28" s="3">
-        <f>E28*(TotalRevenue/50)*0.25</f>
+        <f>(E28*(TotalRevenue/50)*0.25)+(SUM($E$5:E27)*(TotalRevenue/50)*0.25)</f>
         <v/>
       </c>
       <c r="G28" s="3">
-        <f>D28+F28</f>
+        <f>F28</f>
         <v/>
       </c>
       <c r="H28" s="3">
-        <f>G28-C28</f>
+        <f>D28+G28</f>
         <v/>
       </c>
       <c r="I28" s="3">
-        <f>I27+H28</f>
-        <v/>
-      </c>
-      <c r="J28" s="30">
-        <f>IF(I28&lt;0,-I28,0)</f>
+        <f>H28-C28</f>
+        <v/>
+      </c>
+      <c r="J28" s="3">
+        <f>J27+I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="30">
+        <f>IF(J28&lt;0,-J28,0)</f>
         <v/>
       </c>
     </row>
@@ -4424,15 +4525,44 @@
         <f>SUM(F5:F28)</f>
         <v/>
       </c>
+      <c r="G30" s="7">
+        <f>SUM(G5:G28)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>VERIFICATION:</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Total Pre-Sales Payment =</t>
+        </is>
+      </c>
+      <c r="C32" s="3">
+        <f>SUM(F5:F29)</f>
+        <v/>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Should = Total Revenue =</t>
+        </is>
+      </c>
+      <c r="E32" s="3">
+        <f>TotalRevenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>MAX BRIDGE LOAN NEEDED:</t>
         </is>
       </c>
-      <c r="B32" s="32">
-        <f>MAX(J5:J29)</f>
+      <c r="B33" s="32">
+        <f>MAX(K5:K29)</f>
         <v/>
       </c>
     </row>

--- a/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
+++ b/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
@@ -606,7 +606,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2025-11-06 01:03</t>
+          <t>Generated: 2025-11-06 01:08</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="3">
-        <f>(E9*(TotalRevenue/50)*0.25)+(SUM($E$5:E8)*(TotalRevenue/50)*0.25)</f>
+        <f>(E9*(TotalRevenue/50)*0.50)+(SUM($E$5:$E$8)*(TotalRevenue/50)*0.25)</f>
         <v/>
       </c>
       <c r="G9" s="3">
@@ -3687,7 +3687,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="3">
-        <f>E10*(TotalRevenue/50)*0.25</f>
+        <f>E10*(TotalRevenue/50)*0.50</f>
         <v/>
       </c>
       <c r="G10" s="3">
@@ -3731,7 +3731,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="3">
-        <f>E11*(TotalRevenue/50)*0.25</f>
+        <f>E11*(TotalRevenue/50)*0.50</f>
         <v/>
       </c>
       <c r="G11" s="3">
@@ -3775,7 +3775,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="3">
-        <f>E12*(TotalRevenue/50)*0.25</f>
+        <f>E12*(TotalRevenue/50)*0.50</f>
         <v/>
       </c>
       <c r="G12" s="3">
@@ -3819,7 +3819,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="3">
-        <f>E13*(TotalRevenue/50)*0.25</f>
+        <f>(E13*(TotalRevenue/50)*0.75)+(SUM($E$5:$E$12)*(TotalRevenue/50)*0.25)</f>
         <v/>
       </c>
       <c r="G13" s="3">
@@ -3863,7 +3863,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="3">
-        <f>E14*(TotalRevenue/50)*0.25</f>
+        <f>E14*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G14" s="3">
@@ -3907,7 +3907,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="3">
-        <f>E15*(TotalRevenue/50)*0.25</f>
+        <f>E15*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G15" s="3">
@@ -3951,7 +3951,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="3">
-        <f>E16*(TotalRevenue/50)*0.25</f>
+        <f>E16*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G16" s="3">
@@ -3995,7 +3995,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="3">
-        <f>E17*(TotalRevenue/50)*0.25</f>
+        <f>E17*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G17" s="3">
@@ -4039,7 +4039,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="3">
-        <f>E18*(TotalRevenue/50)*0.25</f>
+        <f>E18*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G18" s="3">
@@ -4083,7 +4083,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="3">
-        <f>(E19*(TotalRevenue/50)*0.25)+(SUM($E$5:E18)*(TotalRevenue/50)*0.25)</f>
+        <f>E19*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G19" s="3">
@@ -4127,7 +4127,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="3">
-        <f>E20*(TotalRevenue/50)*0.25</f>
+        <f>E20*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G20" s="3">
@@ -4171,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="3">
-        <f>E21*(TotalRevenue/50)*0.25</f>
+        <f>E21*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G21" s="3">
@@ -4215,7 +4215,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="3">
-        <f>E22*(TotalRevenue/50)*0.25</f>
+        <f>E22*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G22" s="3">
@@ -4259,7 +4259,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="3">
-        <f>E23*(TotalRevenue/50)*0.25</f>
+        <f>E23*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G23" s="3">
@@ -4303,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="3">
-        <f>E24*(TotalRevenue/50)*0.25</f>
+        <f>E24*(TotalRevenue/50)*0.75</f>
         <v/>
       </c>
       <c r="G24" s="3">
@@ -4347,7 +4347,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="3">
-        <f>E25*(TotalRevenue/50)*0.25</f>
+        <f>(E25*(TotalRevenue/50)*1.00)+(SUM($E$5:$E$24)*(TotalRevenue/50)*0.25)</f>
         <v/>
       </c>
       <c r="G25" s="3">
@@ -4391,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="3">
-        <f>E26*(TotalRevenue/50)*0.25</f>
+        <f>E26*(TotalRevenue/50)*1.00</f>
         <v/>
       </c>
       <c r="G26" s="3">
@@ -4435,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="3">
-        <f>E27*(TotalRevenue/50)*0.25</f>
+        <f>E27*(TotalRevenue/50)*1.00</f>
         <v/>
       </c>
       <c r="G27" s="3">
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="3">
-        <f>(E28*(TotalRevenue/50)*0.25)+(SUM($E$5:E27)*(TotalRevenue/50)*0.25)</f>
+        <f>E28*(TotalRevenue/50)*1.00</f>
         <v/>
       </c>
       <c r="G28" s="3">

--- a/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
+++ b/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
@@ -819,7 +819,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2025-11-06 03:25</t>
+          <t>Generated: 2025-11-06 03:56</t>
         </is>
       </c>
     </row>
@@ -39645,7 +39645,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f>TotalHardCosts*0.07</f>
+        <f>TotalHardCosts*0.06</f>
         <v/>
       </c>
       <c r="D13" s="3">
@@ -39705,7 +39705,7 @@
         </is>
       </c>
       <c r="C14" s="3">
-        <f>TotalHardCosts*0.07</f>
+        <f>TotalHardCosts*0.06</f>
         <v/>
       </c>
       <c r="D14" s="3">
@@ -39765,7 +39765,7 @@
         </is>
       </c>
       <c r="C15" s="3">
-        <f>TotalHardCosts*0.06</f>
+        <f>TotalHardCosts*0.05</f>
         <v/>
       </c>
       <c r="D15" s="3">
@@ -39825,7 +39825,7 @@
         </is>
       </c>
       <c r="C16" s="3">
-        <f>TotalHardCosts*0.06</f>
+        <f>TotalHardCosts*0.05</f>
         <v/>
       </c>
       <c r="D16" s="3">
@@ -39885,7 +39885,7 @@
         </is>
       </c>
       <c r="C17" s="3">
-        <f>TotalHardCosts*0.05</f>
+        <f>TotalHardCosts*0.04</f>
         <v/>
       </c>
       <c r="D17" s="3" t="n">
@@ -39944,7 +39944,7 @@
         </is>
       </c>
       <c r="C18" s="3">
-        <f>TotalHardCosts*0.05</f>
+        <f>TotalHardCosts*0.04</f>
         <v/>
       </c>
       <c r="D18" s="3" t="n">
@@ -40003,7 +40003,7 @@
         </is>
       </c>
       <c r="C19" s="3">
-        <f>TotalHardCosts*0.04</f>
+        <f>TotalHardCosts*0.03</f>
         <v/>
       </c>
       <c r="D19" s="3" t="n">
@@ -40062,7 +40062,7 @@
         </is>
       </c>
       <c r="C20" s="3">
-        <f>TotalHardCosts*0.04</f>
+        <f>TotalHardCosts*0.03</f>
         <v/>
       </c>
       <c r="D20" s="3" t="n">
@@ -40357,7 +40357,7 @@
         </is>
       </c>
       <c r="C25" s="3">
-        <f>TotalHardCosts*0.01</f>
+        <f>TotalHardCosts*0.02</f>
         <v/>
       </c>
       <c r="D25" s="3" t="n">
@@ -40416,7 +40416,7 @@
         </is>
       </c>
       <c r="C26" s="3">
-        <f>TotalHardCosts*0.01</f>
+        <f>TotalHardCosts*0.02</f>
         <v/>
       </c>
       <c r="D26" s="3" t="n">
@@ -40475,7 +40475,7 @@
         </is>
       </c>
       <c r="C27" s="3">
-        <f>TotalHardCosts*0.005</f>
+        <f>TotalHardCosts*0.01</f>
         <v/>
       </c>
       <c r="D27" s="3" t="n">
@@ -40534,7 +40534,7 @@
         </is>
       </c>
       <c r="C28" s="3">
-        <f>TotalHardCosts*0.005</f>
+        <f>TotalHardCosts*0.01</f>
         <v/>
       </c>
       <c r="D28" s="3" t="n">

--- a/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
+++ b/NEVO_Tower/outputs/NEVO_Interactive_Budget_V3.xlsx
@@ -36171,6 +36171,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -36178,6 +36179,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -36218,6 +36220,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
@@ -36225,6 +36228,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -36300,6 +36304,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
@@ -36307,6 +36312,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -36472,6 +36478,8 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
@@ -36479,6 +36487,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
@@ -36560,6 +36569,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -36576,6 +36586,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -36612,6 +36623,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
@@ -36619,6 +36631,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -36671,6 +36684,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
@@ -37680,6 +37694,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C6:C28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid Input" error="Please enter a valid cost per square foot" promptTitle="Cost Rate" prompt="Enter cost per GSF (e.g., 45.50)" type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -38076,6 +38095,12 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C6:C20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid Percentage" error="Please enter a percentage between 0% and 100%" promptTitle="Percentage" prompt="Enter as decimal (e.g., 0.05 for 5%)" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -38255,6 +38280,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="E6:E20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Invalid Price" error="Please enter a valid price per square foot" promptTitle="Unit Price" prompt="Enter price per NSF (e.g., 1100.00)" type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
